--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_44.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3762670.894734367</v>
+        <v>3798999.849469504</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101727</v>
+        <v>987.0883260127097</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101727</v>
+        <v>987.0883260127097</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23186206.48727729</v>
+        <v>23185331.97618607</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>1.415908396048882</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -736,19 +736,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>107.3564391497144</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>331.7888056736779</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675552</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -973,16 +973,16 @@
         <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>94.48200024128829</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>374</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>125.9153003789427</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1210,22 +1210,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>172.8521737920021</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1255,16 +1255,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>139.6378117415359</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1447,7 +1447,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -1456,7 +1456,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>3.99961134672543</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>305.4120422616786</v>
+        <v>305.412042261679</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1617,7 +1617,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
         <v>72.84688483418068</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>142.3350019731772</v>
@@ -1659,7 +1659,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U14" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1684,22 +1684,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>200.5295027796754</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,19 +1732,19 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>252.7534963968768</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>98.86273944538755</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N16" t="n">
         <v>155.2579933044718</v>
@@ -1802,16 +1802,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
@@ -1927,19 +1927,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I18" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1969,25 +1969,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T18" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>382.1025822036413</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2039,16 +2039,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S19" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2161,19 +2161,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>177.6137898608468</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S21" t="n">
         <v>131.8202263797057</v>
@@ -2212,19 +2212,19 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968768</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2325,13 +2325,13 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2395,22 +2395,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>200.5295027796757</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490372</v>
+        <v>252.7534963968771</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
@@ -2461,7 +2461,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
         <v>324.9996113467254</v>
@@ -2650,7 +2650,7 @@
         <v>325.021973978874</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2680,10 +2680,10 @@
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>305.4120422616783</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
-        <v>81.3753501231742</v>
+        <v>384.3162518119123</v>
       </c>
       <c r="U27" t="n">
         <v>79.16168051490372</v>
@@ -2753,13 +2753,13 @@
         <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
         <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
@@ -2872,19 +2872,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>200.5295027796754</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>192.2280582198499</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2987,13 +2987,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T32" t="n">
         <v>259.6218731858503</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
@@ -3118,10 +3118,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3154,25 +3154,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968768</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M34" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N34" t="n">
         <v>155.2579933044718</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3340,28 +3340,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>237.1483725282997</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>306.940513035463</v>
       </c>
       <c r="H36" t="n">
         <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>111.3731429098285</v>
@@ -3409,7 +3409,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3516,7 +3516,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H38" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U38" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V38" t="n">
         <v>308.8510241668239</v>
@@ -3583,19 +3583,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>177.5914272286984</v>
       </c>
       <c r="H39" t="n">
-        <v>177.613789860847</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3631,16 +3631,16 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T39" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
         <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>98.86273944538755</v>
@@ -3753,10 +3753,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3814,22 +3814,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>200.5295027796757</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.999611346725456</v>
+        <v>98.96287911935121</v>
       </c>
       <c r="H42" t="n">
         <v>4.021973978873961</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
         <v>180.333570877285</v>
@@ -3874,13 +3874,13 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -4054,10 +4054,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>343.0408141342568</v>
+        <v>264.4122660249097</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
@@ -4105,7 +4105,7 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U45" t="n">
         <v>79.16168051490371</v>
@@ -4114,10 +4114,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
         <v>78.39139276613435</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4175,7 +4175,7 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
         <v>377.7099312598395</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>104.8416377852028</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>54.86731632763319</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>44.42372467121926</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>40.016361431958</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>35.07734253497633</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>29.93969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>399.2096902997726</v>
       </c>
       <c r="L2" t="n">
-        <v>770.4399999999999</v>
+        <v>768.4796902997725</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>768.4796902997726</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>768.4796902997726</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1122.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1405.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1218.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>967.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>735.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>494.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>300.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>187.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>361.9421914987495</v>
+        <v>740.7208178458909</v>
       </c>
       <c r="C3" t="n">
-        <v>361.9421914987495</v>
+        <v>375.9734315372855</v>
       </c>
       <c r="D3" t="n">
-        <v>361.9421914987495</v>
+        <v>375.9734315372855</v>
       </c>
       <c r="E3" t="n">
-        <v>361.9421914987495</v>
+        <v>29.84</v>
       </c>
       <c r="F3" t="n">
-        <v>361.9421914987495</v>
+        <v>29.84</v>
       </c>
       <c r="G3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.1019687139392</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>859.7561604567984</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1387.559152374026</v>
+        <v>1345.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1252.557146342082</v>
+        <v>1210.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1189.437134942722</v>
+        <v>1147.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1184.918504172221</v>
+        <v>1143.281782714996</v>
       </c>
       <c r="U3" t="n">
-        <v>807.1407263944427</v>
+        <v>808.1415749638063</v>
       </c>
       <c r="V3" t="n">
-        <v>792.4834868070486</v>
+        <v>793.4843353764122</v>
       </c>
       <c r="W3" t="n">
-        <v>759.7833424536865</v>
+        <v>760.7841910230501</v>
       </c>
       <c r="X3" t="n">
-        <v>739.7199692765273</v>
+        <v>740.7208178458909</v>
       </c>
       <c r="Y3" t="n">
-        <v>361.9421914987495</v>
+        <v>740.7208178458909</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>353.8993100962325</v>
+        <v>29.84</v>
       </c>
       <c r="C4" t="n">
-        <v>479.9013159146683</v>
+        <v>29.84</v>
       </c>
       <c r="D4" t="n">
-        <v>593.2204600396684</v>
+        <v>143.1591441250001</v>
       </c>
       <c r="E4" t="n">
-        <v>711.0493642510814</v>
+        <v>260.9880483364131</v>
       </c>
       <c r="F4" t="n">
-        <v>835.4103368430169</v>
+        <v>385.3490209283486</v>
       </c>
       <c r="G4" t="n">
-        <v>988.9989978118695</v>
+        <v>482.5491623681919</v>
       </c>
       <c r="H4" t="n">
-        <v>1160.134573790939</v>
+        <v>653.700610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>1386.743548464727</v>
+        <v>880.3632726931805</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.633272693181</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="V4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="W4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="X4" t="n">
-        <v>130.7326717509081</v>
+        <v>29.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>242.1419724299404</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>697.388108133742</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>471.4897954173747</v>
+        <v>394.6673863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>471.4897954173747</v>
+        <v>29.92</v>
       </c>
       <c r="D6" t="n">
-        <v>471.4897954173747</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>125.3563638800892</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4637,52 +4637,52 @@
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>971.7607285971344</v>
       </c>
       <c r="S6" t="n">
-        <v>1294.664012937232</v>
+        <v>844.5735564971923</v>
       </c>
       <c r="T6" t="n">
-        <v>916.8862351594544</v>
+        <v>840.0636831118629</v>
       </c>
       <c r="U6" t="n">
-        <v>916.6883303130679</v>
+        <v>839.8659212042986</v>
       </c>
       <c r="V6" t="n">
-        <v>902.0310907256738</v>
+        <v>825.2086816169045</v>
       </c>
       <c r="W6" t="n">
-        <v>869.3309463723117</v>
+        <v>792.5085372635424</v>
       </c>
       <c r="X6" t="n">
-        <v>849.2675731951525</v>
+        <v>772.4451640863832</v>
       </c>
       <c r="Y6" t="n">
-        <v>849.2675731951525</v>
+        <v>772.4451640863832</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.92</v>
+        <v>576.0083476291953</v>
       </c>
       <c r="C7" t="n">
-        <v>29.92</v>
+        <v>702.0103534476311</v>
       </c>
       <c r="D7" t="n">
-        <v>143.2391441250001</v>
+        <v>815.3294975726312</v>
       </c>
       <c r="E7" t="n">
-        <v>261.0680483364131</v>
+        <v>933.1584017840443</v>
       </c>
       <c r="F7" t="n">
-        <v>385.4290209283486</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="G7" t="n">
-        <v>539.0176818972011</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="H7" t="n">
-        <v>710.1532578762708</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="I7" t="n">
-        <v>881.2025562401257</v>
+        <v>1015.207095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
@@ -4755,13 +4755,13 @@
         <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>201.8109182596774</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>352.841709283871</v>
       </c>
       <c r="Y7" t="n">
-        <v>29.92</v>
+        <v>464.2510099629032</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4798,19 +4798,19 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>451.8183303517587</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M8" t="n">
-        <v>515.8802453266331</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N8" t="n">
-        <v>755.48</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="O8" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1222.526720202428</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="C9" t="n">
-        <v>1222.526720202428</v>
+        <v>724.4391204399794</v>
       </c>
       <c r="D9" t="n">
-        <v>1222.526720202428</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="E9" t="n">
-        <v>876.3932886651428</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F9" t="n">
-        <v>533.3263772127418</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>204.5181553454567</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>1156.805025774064</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>1156.6072638665</v>
       </c>
       <c r="V9" t="n">
-        <v>1275.29023773295</v>
+        <v>1141.950024279106</v>
       </c>
       <c r="W9" t="n">
-        <v>1242.590093379587</v>
+        <v>1109.249879925744</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>1089.186506748585</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253.0866383453244</v>
+        <v>1210.252312640102</v>
       </c>
       <c r="C10" t="n">
-        <v>379.0886441637601</v>
+        <v>1336.254318458537</v>
       </c>
       <c r="D10" t="n">
-        <v>492.4077882887602</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="E10" t="n">
-        <v>610.2366925001733</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="F10" t="n">
-        <v>734.5976650921087</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="G10" t="n">
-        <v>888.1863260609612</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H10" t="n">
-        <v>1059.321902040031</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I10" t="n">
-        <v>1285.930876713819</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>664.1639650109064</v>
       </c>
       <c r="W10" t="n">
-        <v>29.92</v>
+        <v>836.0548832705838</v>
       </c>
       <c r="X10" t="n">
-        <v>29.92</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="Y10" t="n">
-        <v>141.3293006790323</v>
+        <v>1098.49497497381</v>
       </c>
     </row>
     <row r="11">
@@ -5035,13 +5035,13 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L11" t="n">
+        <v>953.2578922784251</v>
+      </c>
+      <c r="M11" t="n">
         <v>1595.767892278425</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2238.277892278425</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>816.9377012410212</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C12" t="n">
-        <v>452.1903149324157</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D12" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E12" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
         <v>60.0226114399994</v>
@@ -5135,13 +5135,13 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S12" t="n">
-        <v>1753.535205884734</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T12" t="n">
-        <v>1671.337882527992</v>
+        <v>1347.095458285567</v>
       </c>
       <c r="U12" t="n">
         <v>1267.13416483617</v>
@@ -5153,10 +5153,10 @@
         <v>1060.180821299454</v>
       </c>
       <c r="X12" t="n">
-        <v>960.319468324315</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y12" t="n">
-        <v>881.1362433080177</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="13">
@@ -5257,7 +5257,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G14" t="n">
         <v>125.5027119537179</v>
@@ -5272,34 +5272,34 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>508.483132485021</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L14" t="n">
-        <v>724.5350810277346</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M14" t="n">
-        <v>724.5350810277346</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N14" t="n">
-        <v>724.5350810277346</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O14" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P14" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U14" t="n">
         <v>1858.092802114017</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>492.6952769985968</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>1073.46537867211</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>727.3319471348245</v>
       </c>
       <c r="F15" t="n">
-        <v>60.02261143999941</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5378,22 +5378,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V15" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>735.9383970570296</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>636.0770440818907</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y15" t="n">
-        <v>556.8938190655933</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="16">
@@ -5436,22 +5436,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N16" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O16" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H17" t="n">
         <v>51.92</v>
@@ -5506,22 +5506,22 @@
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>1009.32297330616</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L17" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M17" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N17" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O17" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P17" t="n">
         <v>2009.555081027735</v>
@@ -5530,28 +5530,28 @@
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>362.0396347695416</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C18" t="n">
-        <v>321.5346727033605</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D18" t="n">
-        <v>294.3248879582063</v>
+        <v>1073.46537867211</v>
       </c>
       <c r="E18" t="n">
-        <v>272.4338806633451</v>
+        <v>727.3319471348245</v>
       </c>
       <c r="F18" t="n">
-        <v>253.6093934533685</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G18" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H18" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
         <v>51.92</v>
@@ -5615,22 +5615,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U18" t="n">
-        <v>1460.720946849539</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V18" t="n">
-        <v>1366.265727464165</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W18" t="n">
-        <v>929.5251790703987</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X18" t="n">
-        <v>829.6638260952598</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y18" t="n">
-        <v>426.2381768365382</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N19" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O19" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q19" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R19" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5743,25 +5743,25 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>1201.938527309012</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L20" t="n">
-        <v>1844.448527309012</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M20" t="n">
-        <v>1844.448527309012</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N20" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1316.525394051095</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C21" t="n">
-        <v>1276.020431984914</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D21" t="n">
-        <v>924.5682229973352</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E21" t="n">
-        <v>578.4347914600496</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F21" t="n">
-        <v>235.3678800076487</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G21" t="n">
-        <v>231.3278685463099</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5846,28 +5846,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R21" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S21" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U21" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V21" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W21" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X21" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y21" t="n">
-        <v>1380.723936118091</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="22">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5983,10 +5983,10 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L23" t="n">
-        <v>1418.446838088717</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M23" t="n">
         <v>1595.767892278425</v>
@@ -6016,16 +6016,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W23" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>992.2829698086707</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C24" t="n">
-        <v>627.5355835000653</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D24" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6083,28 +6083,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S24" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U24" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V24" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W24" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X24" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y24" t="n">
-        <v>1380.723936118092</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6220,22 +6220,22 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L26" t="n">
-        <v>1844.448527309012</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M26" t="n">
-        <v>2238.277892278425</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.277892278425</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="O26" t="n">
-        <v>2399.40799366138</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P26" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1141.180125483446</v>
+        <v>1010.52448325439</v>
       </c>
       <c r="C27" t="n">
-        <v>1100.675163417264</v>
+        <v>970.019521188209</v>
       </c>
       <c r="D27" t="n">
-        <v>1073.46537867211</v>
+        <v>942.8097364430548</v>
       </c>
       <c r="E27" t="n">
-        <v>1051.574371377249</v>
+        <v>920.9187291481936</v>
       </c>
       <c r="F27" t="n">
-        <v>708.507459924848</v>
+        <v>902.094241938217</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2250242210849</v>
+        <v>573.8118062344539</v>
       </c>
       <c r="H27" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6323,25 +6323,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S27" t="n">
-        <v>1753.535205884734</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1671.337882527992</v>
+        <v>1540.682240298936</v>
       </c>
       <c r="U27" t="n">
-        <v>1591.376589078594</v>
+        <v>1460.720946849539</v>
       </c>
       <c r="V27" t="n">
-        <v>1496.92136969322</v>
+        <v>1366.265727464165</v>
       </c>
       <c r="W27" t="n">
-        <v>1384.423245541878</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X27" t="n">
-        <v>1284.56189256674</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y27" t="n">
-        <v>1205.378667550442</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="28">
@@ -6396,10 +6396,10 @@
         <v>819.9299076645212</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6442,7 +6442,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G29" t="n">
         <v>125.5027119537179</v>
@@ -6454,25 +6454,25 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L29" t="n">
-        <v>1418.446838088717</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M29" t="n">
-        <v>2060.956838088718</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N29" t="n">
-        <v>2238.277892278425</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="O29" t="n">
-        <v>2399.40799366138</v>
+        <v>1753.273377636691</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2395.783377636691</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6512,19 +6512,19 @@
         <v>1316.525394051095</v>
       </c>
       <c r="C30" t="n">
-        <v>951.7780077424895</v>
+        <v>951.7780077424893</v>
       </c>
       <c r="D30" t="n">
-        <v>600.3257987549111</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
-        <v>254.1923672176256</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6563,7 +6563,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U30" t="n">
         <v>1766.721857646244</v>
@@ -6578,7 +6578,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>1380.723936118092</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="31">
@@ -6633,7 +6633,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G32" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6691,25 +6691,25 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L32" t="n">
-        <v>668.47</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M32" t="n">
-        <v>668.47</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N32" t="n">
-        <v>1310.98</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O32" t="n">
-        <v>1953.49</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6718,25 +6718,25 @@
         <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="33">
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>343.7981213238219</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C33" t="n">
         <v>127.9478906899915</v>
@@ -6758,10 +6758,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F33" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6800,22 +6800,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W33" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X33" t="n">
-        <v>1135.664736891964</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y33" t="n">
-        <v>732.2390876332428</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="34">
@@ -6858,22 +6858,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N34" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O34" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R34" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C35" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D35" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E35" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G35" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
         <v>51.92</v>
@@ -6931,49 +6931,49 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L35" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="M35" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N35" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O35" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P35" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S35" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W35" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>492.6952769985968</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C36" t="n">
-        <v>127.9478906899915</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D36" t="n">
-        <v>100.7381059448373</v>
+        <v>1248.81064723976</v>
       </c>
       <c r="E36" t="n">
-        <v>78.84709864997603</v>
+        <v>902.6772157024741</v>
       </c>
       <c r="F36" t="n">
-        <v>60.02261143999941</v>
+        <v>559.6103042500731</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866057</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H36" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I36" t="n">
         <v>51.92</v>
@@ -7043,16 +7043,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>1135.664736891965</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>732.239087633243</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="37">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C38" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D38" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E38" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G38" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H38" t="n">
         <v>51.92</v>
@@ -7165,16 +7165,16 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>737.2059437357115</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L38" t="n">
-        <v>953.2578922784251</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M38" t="n">
-        <v>1595.767892278425</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N38" t="n">
         <v>2238.277892278425</v>
@@ -7198,19 +7198,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W38" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X38" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>343.7981213238222</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C39" t="n">
-        <v>303.293159257641</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D39" t="n">
-        <v>276.0833745124868</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E39" t="n">
-        <v>254.1923672176256</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F39" t="n">
-        <v>235.367880007649</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G39" t="n">
-        <v>231.3278685463101</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7274,22 +7274,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U39" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>587.0412413822551</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>487.1798884071161</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y39" t="n">
-        <v>407.9966633908188</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="40">
@@ -7396,7 +7396,7 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
@@ -7408,19 +7408,19 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>1009.32297330616</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M41" t="n">
-        <v>1651.83297330616</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>2222.086939471673</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2418.678945810293</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>992.2829698086707</v>
+        <v>588.6177696982188</v>
       </c>
       <c r="C42" t="n">
-        <v>627.5355835000653</v>
+        <v>223.8703833896134</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872615</v>
+        <v>196.6605986444593</v>
       </c>
       <c r="E42" t="n">
-        <v>78.84709864997603</v>
+        <v>174.769591349598</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>155.9451041396214</v>
       </c>
       <c r="G42" t="n">
         <v>55.98259997866057</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U42" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V42" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W42" t="n">
-        <v>1559.768514109528</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X42" t="n">
-        <v>1459.907161134389</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y42" t="n">
-        <v>1380.723936118092</v>
+        <v>652.8163117652153</v>
       </c>
     </row>
     <row r="43">
@@ -7642,22 +7642,22 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>733.5813277110226</v>
+        <v>1094.928051457287</v>
       </c>
       <c r="L44" t="n">
-        <v>1009.32297330616</v>
+        <v>1310.98</v>
       </c>
       <c r="M44" t="n">
-        <v>1009.32297330616</v>
+        <v>1310.98</v>
       </c>
       <c r="N44" t="n">
-        <v>1651.83297330616</v>
+        <v>1310.98</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>1953.49</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>668.0405455662462</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C45" t="n">
-        <v>321.5346727033605</v>
+        <v>645.7770969457847</v>
       </c>
       <c r="D45" t="n">
         <v>294.3248879582063</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095641</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V45" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W45" t="n">
-        <v>1235.526089867103</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X45" t="n">
-        <v>811.4223126495401</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y45" t="n">
-        <v>732.2390876332428</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="46">
@@ -7803,19 +7803,19 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
         <v>464.3167555675508</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>320.3286984924623</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748743</v>
+        <v>307.6565929648241</v>
       </c>
       <c r="M2" t="n">
-        <v>772.4711016975159</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>299.0534951208153</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8055,7 +8055,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N3" t="n">
-        <v>485.4085271713503</v>
+        <v>481.6508651829305</v>
       </c>
       <c r="O3" t="n">
         <v>382.6817988009037</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>235.5012052109774</v>
+        <v>234.1880104510425</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>374.4816735941929</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>181.6174062160024</v>
       </c>
       <c r="M8" t="n">
-        <v>472.2608914614128</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N8" t="n">
-        <v>646.1026208280709</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>374.4816735941929</v>
       </c>
       <c r="P8" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>179.5731479057567</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="M11" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>202.9328222164582</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O14" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>278.5269147425628</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>430.7657085427136</v>
+        <v>216.0870636498471</v>
       </c>
       <c r="M17" t="n">
         <v>301.434429149855</v>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>301.434429149855</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N20" t="n">
-        <v>628.2994929102651</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,13 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L23" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>480.5466050990546</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
         <v>879.4920535472222</v>
@@ -9863,25 +9863,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>699.241868512898</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N26" t="n">
         <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>409.6042294964216</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.48346824708341</v>
+        <v>225.7224807352743</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L32" t="n">
-        <v>146.3014272389486</v>
+        <v>236.2045428832664</v>
       </c>
       <c r="M32" t="n">
         <v>301.434429149855</v>
       </c>
       <c r="N32" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O32" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,10 +10574,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L35" t="n">
-        <v>60.29262328527625</v>
+        <v>179.5731479057567</v>
       </c>
       <c r="M35" t="n">
         <v>950.4344291498551</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>433.9659648939233</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>699.241868512898</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11051,13 +11051,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
-        <v>17.50927946942295</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M41" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N41" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>202.5956441962828</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,25 +11285,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>364.9966906527919</v>
       </c>
       <c r="L44" t="n">
-        <v>60.29262328527625</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>301.434429149855</v>
       </c>
       <c r="N44" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.927393539208561</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24371,7 +24371,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8382458495973992</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24611,13 +24611,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>0.8382458495973424</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976959</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26033,7 +26033,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>892178.9310546662</v>
+        <v>891890.0617539417</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1710774.007270852</v>
+        <v>1710591.902429134</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2529369.083487039</v>
+        <v>2529186.978645321</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3347516.760067973</v>
+        <v>3347417.036726255</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4166098.759648907</v>
+        <v>4165999.036307188</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4984680.759229839</v>
+        <v>4984581.035888121</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5803262.758810768</v>
+        <v>5803163.03546905</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6621844.758391697</v>
+        <v>6621745.035049979</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7440426.757972627</v>
+        <v>7440327.034630908</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8259008.757553556</v>
+        <v>8258909.034211838</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9077590.757134493</v>
+        <v>9077491.033792775</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9896172.756715432</v>
+        <v>9896073.033373713</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10714754.75629637</v>
+        <v>10714655.03295465</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11533336.75587731</v>
+        <v>11533237.03253559</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12351918.75545825</v>
+        <v>12351819.03211653</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385145.981787561</v>
       </c>
       <c r="C2" t="n">
         <v>1385314.744365854</v>
@@ -26281,19 +26281,19 @@
         <v>1385292.614675425</v>
       </c>
       <c r="F2" t="n">
-        <v>1385292.614675426</v>
+        <v>1385292.614675425</v>
       </c>
       <c r="G2" t="n">
         <v>1385292.614675425</v>
       </c>
       <c r="H2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675426</v>
       </c>
       <c r="I2" t="n">
         <v>1385292.614675425</v>
       </c>
       <c r="J2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675426</v>
       </c>
       <c r="K2" t="n">
         <v>1385292.614675425</v>
@@ -26305,7 +26305,7 @@
         <v>1385292.614675425</v>
       </c>
       <c r="N2" t="n">
-        <v>1385292.614675425</v>
+        <v>1385292.614675426</v>
       </c>
       <c r="O2" t="n">
         <v>1385292.614675425</v>
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049333</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495912</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562992</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>518161.4096990888</v>
+        <v>524050.4752826281</v>
       </c>
       <c r="C6" t="n">
-        <v>751268.3318865778</v>
+        <v>757612.441116263</v>
       </c>
       <c r="D6" t="n">
-        <v>753279.9793024015</v>
+        <v>759975.5296450668</v>
       </c>
       <c r="E6" t="n">
-        <v>231859.0858792503</v>
+        <v>239297.0770096045</v>
       </c>
       <c r="F6" t="n">
-        <v>823095.148697474</v>
+        <v>829558.1398278271</v>
       </c>
       <c r="G6" t="n">
-        <v>824783.5382191261</v>
+        <v>831246.5293494804</v>
       </c>
       <c r="H6" t="n">
-        <v>826474.2711290888</v>
+        <v>832937.2622594435</v>
       </c>
       <c r="I6" t="n">
-        <v>828167.3643296359</v>
+        <v>834630.3554599901</v>
       </c>
       <c r="J6" t="n">
-        <v>441414.8349445608</v>
+        <v>448229.8260749155</v>
       </c>
       <c r="K6" t="n">
-        <v>831560.7003233945</v>
+        <v>837671.6914537483</v>
       </c>
       <c r="L6" t="n">
-        <v>833260.9780457384</v>
+        <v>839723.9691760927</v>
       </c>
       <c r="M6" t="n">
-        <v>738163.6859257062</v>
+        <v>744626.6770560601</v>
       </c>
       <c r="N6" t="n">
-        <v>836668.8420164698</v>
+        <v>843131.8331468244</v>
       </c>
       <c r="O6" t="n">
-        <v>581576.4646149321</v>
+        <v>588039.4557452863</v>
       </c>
       <c r="P6" t="n">
-        <v>840086.5722665153</v>
+        <v>846549.5633968693</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27515,25 +27515,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37.7170900917086</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>68.40697861481078</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27606,7 +27606,7 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>343.0400961869588</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,13 +27615,13 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>395.1372930982029</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>349.2746269966814</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27752,25 +27752,25 @@
         <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>245.1542420965886</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>159.5184388018133</v>
+      </c>
+      <c r="S6" t="n">
+        <v>336.5335580762346</v>
+      </c>
+      <c r="T6" t="n">
         <v>400</v>
-      </c>
-      <c r="S6" t="n">
-        <v>400</v>
-      </c>
-      <c r="T6" t="n">
-        <v>30.47344446279683</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27840,25 +27840,25 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>357.2603242763692</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I7" t="n">
-        <v>343.8791148384516</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27989,25 +27989,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>157.1970077340416</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>264.8269629099402</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28071,31 +28071,31 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>335.2460937636845</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>124.0957664680556</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28226,7 +28226,7 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -28235,7 +28235,7 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28271,16 +28271,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>147.4081841180271</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28438,7 +28438,7 @@
         <v>321</v>
       </c>
       <c r="U14" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V14" t="n">
         <v>321</v>
@@ -28463,19 +28463,19 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
@@ -28517,13 +28517,13 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
         <v>321</v>
@@ -28636,7 +28636,7 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I17" t="n">
         <v>96.76634561233286</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
@@ -28706,19 +28706,19 @@
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>321</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28754,19 +28754,19 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>18.05909831126235</v>
+        <v>321</v>
       </c>
       <c r="V18" t="n">
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
         <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28940,19 +28940,19 @@
         <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
       </c>
       <c r="H21" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
       <c r="I21" t="n">
         <v>191.6509141932353</v>
@@ -28982,7 +28982,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>321</v>
@@ -28991,19 +28991,19 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="V21" t="n">
         <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29104,13 +29104,13 @@
         <v>321</v>
       </c>
       <c r="F23" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G23" t="n">
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29174,16 +29174,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29219,7 +29219,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>321</v>
@@ -29228,7 +29228,7 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>321</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="V24" t="n">
         <v>321</v>
@@ -29240,7 +29240,7 @@
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29420,7 +29420,7 @@
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -29429,7 +29429,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29459,10 +29459,10 @@
         <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>147.4081841180273</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>18.05909831126195</v>
       </c>
       <c r="U27" t="n">
         <v>321</v>
@@ -29651,13 +29651,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29854,7 +29854,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S32" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T32" t="n">
         <v>321</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
@@ -29939,19 +29939,19 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
@@ -30058,7 +30058,7 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I35" t="n">
         <v>96.76634561233286</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30119,28 +30119,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>321</v>
+        <v>18.05909831126235</v>
       </c>
       <c r="H36" t="n">
         <v>321</v>
       </c>
       <c r="I36" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30179,7 +30179,7 @@
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W36" t="n">
         <v>321</v>
@@ -30188,7 +30188,7 @@
         <v>321</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
@@ -30295,7 +30295,7 @@
         <v>321</v>
       </c>
       <c r="H38" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I38" t="n">
         <v>96.76634561233286</v>
@@ -30334,7 +30334,7 @@
         <v>321</v>
       </c>
       <c r="U38" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V38" t="n">
         <v>321</v>
@@ -30362,19 +30362,19 @@
         <v>321</v>
       </c>
       <c r="D39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="H39" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="I39" t="n">
         <v>191.6509141932353</v>
@@ -30410,16 +30410,16 @@
         <v>321</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U39" t="n">
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X39" t="n">
         <v>321</v>
@@ -30532,10 +30532,10 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30593,22 +30593,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
         <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="H42" t="n">
         <v>321</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>321</v>
@@ -30653,13 +30653,13 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30833,10 +30833,10 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>18.0590983112624</v>
+        <v>96.68764642060955</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30884,7 +30884,7 @@
         <v>321</v>
       </c>
       <c r="T45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>321</v>
@@ -30893,10 +30893,10 @@
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>373.9999999999999</v>
+        <v>373</v>
       </c>
       <c r="M2" t="n">
-        <v>300.2102102361031</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>298.5718215266224</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>188.4896145353295</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34892,22 +34892,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>98.18196105034679</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>101.8309815665739</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>300.210210236103</v>
+        <v>299.5314174862184</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>374</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>59.25677413017286</v>
+      </c>
+      <c r="Q5" t="n">
         <v>374</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>58.67867865278593</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35126,25 +35126,25 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>82.87746830862726</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>172.7770690543989</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,22 +35220,22 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824119</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>246.9608132511783</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>242.0199542155221</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P8" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,25 +35357,25 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>49.70987570812906</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>101.830981566574</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35405,19 +35405,19 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,16 +35457,16 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L11" t="n">
-        <v>397.8074393630432</v>
+        <v>221.895519765053</v>
       </c>
       <c r="M11" t="n">
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35694,25 +35694,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>378.8447418144482</v>
+        <v>179.1121759491997</v>
       </c>
       <c r="L14" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O14" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>454.4388343405527</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>434.3213551071335</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -35946,7 +35946,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P17" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q17" t="n">
         <v>592.3686050224903</v>
@@ -36080,7 +36080,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H19" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I19" t="n">
         <v>163.0214951995539</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L20" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M20" t="n">
+        <v>490.597359871433</v>
+      </c>
+      <c r="N20" t="n">
         <v>649</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>397.807439363043</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36405,13 +36405,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
+        <v>609.8778844919133</v>
+      </c>
+      <c r="L23" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M23" t="n">
         <v>649</v>
-      </c>
-      <c r="L23" t="n">
-        <v>649</v>
-      </c>
-      <c r="M23" t="n">
-        <v>179.1121759491996</v>
       </c>
       <c r="N23" t="n">
         <v>649</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,25 +36642,25 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L26" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>421.6280856303014</v>
+      </c>
+      <c r="P26" t="n">
         <v>649</v>
       </c>
-      <c r="M26" t="n">
-        <v>397.807439363043</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>162.757678164601</v>
-      </c>
-      <c r="P26" t="n">
-        <v>198.5777841804241</v>
-      </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L29" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>179.1121759491994</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>202.2390124881909</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>364.535718696235</v>
+        <v>454.4388343405528</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P32" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37353,10 +37353,10 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>278.5269147425627</v>
+        <v>397.8074393630432</v>
       </c>
       <c r="M35" t="n">
         <v>649</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
-        <v>609.8778844919133</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>397.807439363043</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37830,13 +37830,13 @@
         <v>649</v>
       </c>
       <c r="L41" t="n">
-        <v>235.7435709267094</v>
+        <v>649</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>649</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38064,25 +38064,25 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>540.9086102507819</v>
       </c>
       <c r="L44" t="n">
-        <v>278.5269147425627</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>649</v>
       </c>
-      <c r="O44" t="n">
-        <v>162.757678164601</v>
-      </c>
       <c r="P44" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
